--- a/Ver3/testdata/エクセル/real_article_dataset_v2.xlsx
+++ b/Ver3/testdata/エクセル/real_article_dataset_v2.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9733118985f6bf19/Desktop/datamix/講義/05_インテグレーションステップ/fake-news-checker/Ver3/testdata/エクセル/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8644BF3-E5FB-4CF7-82F8-483FFBC7F74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="220" documentId="8_{EFA7919F-0225-4BC1-9D45-586A78897045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97F0E9B4-5A1A-4B2A-846D-3842475C12B7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7FC57CB8-58B8-4D11-BAE9-ABF3B8D390BE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3A631B86-80AE-45B4-83A3-F944338A8872}"/>
   </bookViews>
   <sheets>
     <sheet name="real_article_dataset_v2" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">real_article_dataset_v2!$A$1:$E$101</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="216">
   <si>
     <t>id</t>
   </si>
@@ -88,132 +91,111 @@
     <t>positive-accurate-08-jid220707</t>
   </si>
   <si>
-    <t>G7が日本円で81兆円に相当する6千億ドルを、途上国のインフラ投資に回す</t>
+    <t>史上最短の戦争は1時間も続かなかった。</t>
+  </si>
+  <si>
+    <t>positive-accurate-09-infact220821</t>
+  </si>
+  <si>
+    <t>クリーブランド・インディアンスは、クリーブランド・ガーディアンズに名称変更した。</t>
+  </si>
+  <si>
+    <t>positive-accurate-10-wasegg220709-2</t>
+  </si>
+  <si>
+    <t>パラオは750万ドルの合意に基づき、米国から強制送還された最大75人を受け入れることに同意した。</t>
+  </si>
+  <si>
+    <t>政治</t>
+  </si>
+  <si>
+    <t>positive-accurate-11-litmus221003</t>
+  </si>
+  <si>
+    <t>金星では「1日」が「1年」より長い。</t>
+  </si>
+  <si>
+    <t>positive-accurate-12-mainichi230505</t>
+  </si>
+  <si>
+    <t>日本では子供は減っているが、大学は増えている。</t>
+  </si>
+  <si>
+    <t>positive-accurate-13-litmus230706</t>
+  </si>
+  <si>
+    <t>住民税非課税世帯の４分の３は高齢者である。</t>
+  </si>
+  <si>
+    <t>positive-accurate-14-post-23899</t>
+  </si>
+  <si>
+    <t>大谷翔平は、メジャーリーグ史上初めてシーズン50本塁打50盗塁を達成した。</t>
+  </si>
+  <si>
+    <t>positive-accurate-15-japan-experimental-forestry</t>
+  </si>
+  <si>
+    <t>日本には円形の実験林が存在する</t>
+  </si>
+  <si>
+    <t>positive-accurate-16-japanese-robotic-monster-wolves</t>
+  </si>
+  <si>
+    <t>日本のある町では、住民からクマとの遭遇や目撃情報が増加しているとの報告を受け、オオカミに偽装したロボット2体を使ってクマを地域から追い払った。</t>
+  </si>
+  <si>
+    <t>positive-accurate-17-toyota-city-japan-name</t>
+  </si>
+  <si>
+    <t>日本の豊田市は、自動車メーカーであるトヨタ自動車にちなんで名付けられた。</t>
+  </si>
+  <si>
+    <t>positive-accurate-18-square-watermelon</t>
+  </si>
+  <si>
+    <t>日本で作られている四角いスイカは実在し、観賞用や贈答用として栽培されている。</t>
+  </si>
+  <si>
+    <t>positive-accurate-19-ronald-mcdonald-name-japan</t>
+  </si>
+  <si>
+    <t>ファストフードチェーン・マクドナルドのマスコットキャラクターは日本ではドナルド・マクドナルドの名前で呼ばれているが、英語の原名はロナルド・マクドナルドである。</t>
+  </si>
+  <si>
+    <t>positive-accurate-20-photos-japan-orca</t>
+  </si>
+  <si>
+    <t>北海道沖で白いシャチの写真が撮影された</t>
+  </si>
+  <si>
+    <t>positive-mostly-accurate-01-ainu-dance-filmed-1919</t>
+  </si>
+  <si>
+    <t>ほぼ正確</t>
+  </si>
+  <si>
+    <t>アイヌの踊りが1919年に撮影され、カラー映像で保存されていた。</t>
+  </si>
+  <si>
+    <t>positive-mostly-accurate-02-real-image-of-jovial-swedish-people-despite-train-station-flooding-caused-by-typhoon</t>
+  </si>
+  <si>
+    <t>positive-mostly-accurate-03-almost-accurate-claim-iaea-not-verifying-filtration-performance-of-contaminated-water</t>
+  </si>
+  <si>
+    <t>positive-mostly-accurate-04-infact200912</t>
+  </si>
+  <si>
+    <t>positive-mostly-accurate-06-jid211024-1</t>
+  </si>
+  <si>
+    <t>positive-mostly-accurate-07-jid211029-01</t>
   </si>
   <si>
     <t>金融</t>
   </si>
   <si>
-    <t>positive-accurate-09-infact220821</t>
-  </si>
-  <si>
-    <t>クリーブランド・インディアンスは、クリーブランド・ガーディアンズに名称変更した。</t>
-  </si>
-  <si>
-    <t>positive-accurate-10-wasegg220709-2</t>
-  </si>
-  <si>
-    <t>パラオはアメリカを追放される不法移民を最大75人受け入れることに合意した。</t>
-  </si>
-  <si>
-    <t>政治</t>
-  </si>
-  <si>
-    <t>positive-accurate-11-litmus221003</t>
-  </si>
-  <si>
-    <t>金星では「1日」が「1年」より長い。</t>
-  </si>
-  <si>
-    <t>positive-accurate-12-mainichi230505</t>
-  </si>
-  <si>
-    <t>日本では子供は減っているが、大学は増えている。</t>
-  </si>
-  <si>
-    <t>positive-accurate-13-litmus230706</t>
-  </si>
-  <si>
-    <t>住民税非課税世帯の４分の３は高齢者である。</t>
-  </si>
-  <si>
-    <t>positive-accurate-14-post-23899</t>
-  </si>
-  <si>
-    <t>大谷翔平は、メジャーリーグ史上初めてシーズン50本塁打50盗塁を達成した。</t>
-  </si>
-  <si>
-    <t>positive-accurate-15-japan-experimental-forestry</t>
-  </si>
-  <si>
-    <t>日本には円形の実験林が存在する</t>
-  </si>
-  <si>
-    <t>positive-accurate-16-japanese-robotic-monster-wolves</t>
-  </si>
-  <si>
-    <t>日本のある町では、住民からクマとの遭遇や目撃情報が増加しているとの報告を受け、オオカミに偽装したロボット2体を使ってクマを地域から追い払った。</t>
-  </si>
-  <si>
-    <t>positive-accurate-17-toyota-city-japan-name</t>
-  </si>
-  <si>
-    <t>日本の豊田市は、自動車メーカーであるトヨタ自動車にちなんで名付けられた。</t>
-  </si>
-  <si>
-    <t>positive-accurate-18-square-watermelon</t>
-  </si>
-  <si>
-    <t>日本で作られている四角いスイカは実在し、観賞用や贈答用として栽培されている。</t>
-  </si>
-  <si>
-    <t>positive-accurate-19-ronald-mcdonald-name-japan</t>
-  </si>
-  <si>
-    <t>ファストフードチェーン・マクドナルドのマスコットキャラクターは日本ではドナルド・マクドナルドの名前で呼ばれているが、英語の原名はロナルド・マクドナルドである。</t>
-  </si>
-  <si>
-    <t>positive-accurate-20-photos-japan-orca</t>
-  </si>
-  <si>
-    <t>北海道沖で白いシャチの写真が撮影された</t>
-  </si>
-  <si>
-    <t>positive-mostly-accurate-01-ainu-dance-filmed-1919</t>
-  </si>
-  <si>
-    <t>ほぼ正確</t>
-  </si>
-  <si>
-    <t>アイヌの踊りが1919年に撮影され、カラー映像で保存されていた。</t>
-  </si>
-  <si>
-    <t>positive-mostly-accurate-02-real-image-of-jovial-swedish-people-despite-train-station-flooding-caused-by-typhoon</t>
-  </si>
-  <si>
-    <t>国際オリンピック委員会（IOC）は、2020年の東京オリンピック競技大会において、「ブラック・ライブズ・マター」の文字が入った衣服の着用を禁止した。</t>
-  </si>
-  <si>
-    <t>positive-mostly-accurate-03-almost-accurate-claim-iaea-not-verifying-filtration-performance-of-contaminated-water</t>
-  </si>
-  <si>
-    <t>国際原子力機関（IAEA）、汚染水をろ過する多核種除去設備（ALPS）の性能検証を一度もしていなかった</t>
-  </si>
-  <si>
-    <t>positive-mostly-accurate-04-infact200912</t>
-  </si>
-  <si>
-    <t>愛知県の大村秀章知事のリコールに賛同した署名者の個人情報は公開される</t>
-  </si>
-  <si>
-    <t>positive-mostly-accurate-05-infact211023-3</t>
-  </si>
-  <si>
-    <t>ニューヨーク市の新型コロナウイルスによる死亡率は、東京の250倍高い</t>
-  </si>
-  <si>
-    <t>positive-mostly-accurate-06-jid211024-1</t>
-  </si>
-  <si>
-    <t>スウェーデンは、電力と暖房を生産する廃棄物発電所の燃料となる廃棄物が不足しているため、他国から廃棄物を輸入している。</t>
-  </si>
-  <si>
-    <t>positive-mostly-accurate-07-jid211029-01</t>
-  </si>
-  <si>
-    <t>マサチューセッツ州の有権者は、100万ドルを超える所得に対する4％の追加税を承認し、これにより15億ドルの歳入が得られた。</t>
-  </si>
-  <si>
     <t>positive-mostly-accurate-08-asahi211116-2</t>
   </si>
   <si>
@@ -223,9 +205,6 @@
     <t>positive-mostly-accurate-09-infact211217-1</t>
   </si>
   <si>
-    <t>2021年に米国に報告されたワクチン接種後の心筋炎の報告数が、前年の260倍以上になっている</t>
-  </si>
-  <si>
     <t>positive-mostly-accurate-10-infact220704</t>
   </si>
   <si>
@@ -235,21 +214,12 @@
     <t>positive-mostly-accurate-11-infact220706-2</t>
   </si>
   <si>
-    <t>山本太郎代表「安倍さんが総理大臣時代に、消費税増税分の二割程度は社会保障に使ったけど、八割を借金返しに使ったと言った」</t>
-  </si>
-  <si>
     <t>positive-mostly-accurate-12-infact220708</t>
   </si>
   <si>
-    <t>公明党議員「公示前のタスキは、禁じられています」</t>
-  </si>
-  <si>
     <t>positive-mostly-accurate-13-infact220823</t>
   </si>
   <si>
-    <t>志位和夫委員長「大学の入学金制度は『世界で日本にしかない』」</t>
-  </si>
-  <si>
     <t>positive-mostly-accurate-14-bfj230313</t>
   </si>
   <si>
@@ -259,37 +229,16 @@
     <t>positive-mostly-accurate-15-post-22724</t>
   </si>
   <si>
-    <t>1月9日、ファウチ博士は米下院特別小委員会で、６フィートの社会的距離のルールは完全にでっち上げであり、科学的根拠はゼロであったことを認めた。</t>
-  </si>
-  <si>
-    <t>positive-mostly-accurate-16-post-22836</t>
-  </si>
-  <si>
-    <t>WHO(世界保健機関)のテドロス事務局長「WHOは新型コロナウイルスパンデミックの際、誰にも何も強制していない。」</t>
-  </si>
-  <si>
     <t>positive-mostly-accurate-17-23435</t>
   </si>
   <si>
-    <t>200万と語学力が無いとスイスで安楽死出来ません</t>
-  </si>
-  <si>
     <t>positive-mostly-accurate-18-kobe-pension-standardly-nontaxable</t>
   </si>
   <si>
-    <t>住民税非課税世帯への給付が繰り返されるが、年金受給者は控除により非課税になりやすく標準的には非課税です。「年金控除＋非課税世帯への給付」の組合せにより、結果として高齢者優遇となり、現役世代との間に著しい不公平が生じています。裁量的なバラマキは止め、一律の支援制度へと改めるべきです</t>
-  </si>
-  <si>
     <t>positive-mostly-accurate-19-japanese-electric-car-200km-single-charge</t>
   </si>
   <si>
-    <t>日本の自動車メーカーは1949年に、1回の充電で200km走行できる電気自動車を開発した。</t>
-  </si>
-  <si>
     <t>positive-mostly-accurate-20-blobfish-natural-environment</t>
-  </si>
-  <si>
-    <t>バイデン政権はマドゥロに2500万ドルの懸賞金をかけた</t>
   </si>
   <si>
     <t>jfc-hold-01-yokohama-team-mirai-election-fraud-unfounded</t>
@@ -687,6 +636,182 @@
   </si>
   <si>
     <t>天皇陛下や上皇陛下がジェフリー・エプスタイン氏と一緒に写っている写真は本物だ。</t>
+  </si>
+  <si>
+    <t>変更</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>20世紀末に活躍した三大テノールとは、ルチアーノ・パヴァロッティ、プラシド・ドミンゴ、ホセ・カレーライスの3名である。</t>
+    <rPh sb="2" eb="4">
+      <t>セイキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カツヤク</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>メージャーリーグのシーズン最多安打記録は、イチローの261安打である。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>バイデン政権はマドゥロに2500万ドルの懸賞金をかけた</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>日本の自動車メーカーは1949年に、1回の充電で400km走行できる電気自動車を開発した。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>世界最高峰のエベレストの標高は8818mである。</t>
+    <rPh sb="0" eb="5">
+      <t>セカイサイコウホウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウコウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>天空の城ラピュタはスタジオジブリの初制作アニメ映画であり、1987年に公開された。</t>
+    <rPh sb="0" eb="2">
+      <t>テンクウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>エイガ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>日本国憲法はアメリカが作った憲法である。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>一般</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ペンギンはみんな南極に住んでいる。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>マサチューセッツ州の有権者は、100万ドルを超える所得に対する4％の追加税を承認し、これにより2024年度に15億ドルの歳入が得られた。</t>
+    <rPh sb="51" eb="53">
+      <t>ネンド</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>大谷翔平と同学年のメージャーリーガーは鈴木誠である。</t>
+    <rPh sb="0" eb="4">
+      <t>オオタニショウヘイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ドウガクネン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>スズキ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>マコト</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>織田信長は本能寺の変で明智光秀に殺された。</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>通算本塁打数の世界記録は王貞治の858本である。</t>
+    <rPh sb="5" eb="6">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>オウサダハル</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ホン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>アメリカの国土面積は日本の20倍である。</t>
+    <rPh sb="5" eb="9">
+      <t>コクドメンセキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ニホン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>X JAPANは1988年にアルバム『BLUE BLOOD』でメジャー・デビューした。</t>
+    <rPh sb="12" eb="13">
+      <t>ネン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>大政奉還で江戸幕府は終焉を迎え、明治時代に移った。</t>
+    <rPh sb="10" eb="12">
+      <t>シュウエン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ムカ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>メイジジダイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ウツ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>玉置浩二は、日本のシンガーソングライター、ロックバンド完全地帯のボーカリストで、北海道旭川市出身である。</t>
+    <rPh sb="2" eb="4">
+      <t>コウジ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カンゼン</t>
+    </rPh>
+    <rPh sb="40" eb="43">
+      <t>ホッカイドウ</t>
+    </rPh>
+    <rPh sb="43" eb="46">
+      <t>アサヒカワシ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>シュッシン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>positive-mostly-accurate-16-post-22836</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>positive-mostly-accurate-05-infact211023-3</t>
+    <phoneticPr fontId="18"/>
   </si>
 </sst>
 </file>
@@ -854,7 +979,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1032,6 +1157,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1283,8 +1414,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1640,1425 +1771,1478 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309E76A3-EA38-4660-8A02-265ADD705E37}">
-  <dimension ref="A1:D101"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA116F4C-F3D0-4267-A97A-F82C571EBE6D}">
+  <dimension ref="A1:E101"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="5.19921875" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>5</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>5</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
         <v>5</v>
       </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
+      <c r="D11" t="s">
         <v>26</v>
       </c>
-      <c r="B11" t="s">
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
         <v>5</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
         <v>27</v>
       </c>
-      <c r="D11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
         <v>5</v>
       </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
         <v>5</v>
       </c>
-      <c r="C13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="D15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
         <v>5</v>
       </c>
-      <c r="C14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
         <v>5</v>
       </c>
-      <c r="C15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="D17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" t="s">
         <v>5</v>
       </c>
-      <c r="C16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="D18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" t="s">
         <v>5</v>
       </c>
-      <c r="C17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="D19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" t="s">
         <v>5</v>
       </c>
-      <c r="C18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="D20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
         <v>5</v>
       </c>
-      <c r="C19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
+      <c r="D21" t="s">
         <v>47</v>
       </c>
-      <c r="B21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
         <v>48</v>
       </c>
-      <c r="D21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
+      <c r="C22" t="s">
         <v>49</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D22" t="s">
         <v>50</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
         <v>51</v>
       </c>
-      <c r="D22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
+      <c r="C23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
         <v>52</v>
       </c>
-      <c r="B23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="C24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25" t="s">
         <v>53</v>
       </c>
-      <c r="D23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
+      <c r="C25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26" t="s">
+        <v>215</v>
+      </c>
+      <c r="C26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27" t="s">
         <v>54</v>
       </c>
-      <c r="B24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="C27" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28" t="s">
         <v>55</v>
       </c>
-      <c r="D24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
+      <c r="C28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E28" t="s">
         <v>56</v>
       </c>
-      <c r="B25" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" t="s">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
         <v>57</v>
       </c>
-      <c r="D25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
+      <c r="C29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" t="s">
         <v>58</v>
       </c>
-      <c r="B26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="B30" t="s">
         <v>59</v>
       </c>
-      <c r="D26" t="s">
+      <c r="C30" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A32">
+        <v>1</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A33">
+        <v>1</v>
+      </c>
+      <c r="B33" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B35" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <v>1</v>
+      </c>
+      <c r="B36" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" t="s">
+        <v>49</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A37">
+        <v>1</v>
+      </c>
+      <c r="B37" t="s">
+        <v>214</v>
+      </c>
+      <c r="C37" t="s">
+        <v>49</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A38">
+        <v>1</v>
+      </c>
+      <c r="B38" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A39">
+        <v>1</v>
+      </c>
+      <c r="B39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" t="s">
+        <v>49</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E39" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A40">
+        <v>1</v>
+      </c>
+      <c r="B40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" t="s">
+        <v>49</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B41" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" t="s">
+        <v>199</v>
+      </c>
+      <c r="E41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B42" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" t="s">
+        <v>73</v>
+      </c>
+      <c r="D42" t="s">
+        <v>74</v>
+      </c>
+      <c r="E42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B43" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" t="s">
+        <v>73</v>
+      </c>
+      <c r="D43" t="s">
+        <v>76</v>
+      </c>
+      <c r="E43" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>66</v>
-      </c>
-      <c r="B30" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" t="s">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44" t="s">
+        <v>73</v>
+      </c>
+      <c r="D44" t="s">
+        <v>78</v>
+      </c>
+      <c r="E44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" t="s">
+        <v>73</v>
+      </c>
+      <c r="D45" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>81</v>
+      </c>
+      <c r="C46" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
+        <v>83</v>
+      </c>
+      <c r="C47" t="s">
+        <v>73</v>
+      </c>
+      <c r="D47" t="s">
+        <v>84</v>
+      </c>
+      <c r="E47" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B48" t="s">
+        <v>85</v>
+      </c>
+      <c r="C48" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" t="s">
+        <v>86</v>
+      </c>
+      <c r="E48" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" t="s">
+        <v>89</v>
+      </c>
+      <c r="E49" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B50" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" t="s">
+        <v>73</v>
+      </c>
+      <c r="D50" t="s">
+        <v>91</v>
+      </c>
+      <c r="E50" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B51" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" t="s">
+        <v>73</v>
+      </c>
+      <c r="D51" t="s">
+        <v>93</v>
+      </c>
+      <c r="E51" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B52" t="s">
+        <v>94</v>
+      </c>
+      <c r="C52" t="s">
+        <v>73</v>
+      </c>
+      <c r="D52" t="s">
+        <v>95</v>
+      </c>
+      <c r="E52" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B53" t="s">
+        <v>96</v>
+      </c>
+      <c r="C53" t="s">
+        <v>73</v>
+      </c>
+      <c r="D53" t="s">
+        <v>97</v>
+      </c>
+      <c r="E53" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B54" t="s">
+        <v>98</v>
+      </c>
+      <c r="C54" t="s">
+        <v>73</v>
+      </c>
+      <c r="D54" t="s">
+        <v>99</v>
+      </c>
+      <c r="E54" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B55" t="s">
+        <v>100</v>
+      </c>
+      <c r="C55" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55" t="s">
+        <v>101</v>
+      </c>
+      <c r="E55" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B56" t="s">
+        <v>102</v>
+      </c>
+      <c r="C56" t="s">
+        <v>73</v>
+      </c>
+      <c r="D56" t="s">
+        <v>103</v>
+      </c>
+      <c r="E56" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>68</v>
-      </c>
-      <c r="B31" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" t="s">
-        <v>69</v>
-      </c>
-      <c r="D31" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>70</v>
-      </c>
-      <c r="B32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" t="s">
-        <v>71</v>
-      </c>
-      <c r="D32" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>72</v>
-      </c>
-      <c r="B33" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" t="s">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>104</v>
+      </c>
+      <c r="C57" t="s">
         <v>73</v>
       </c>
-      <c r="D33" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>74</v>
-      </c>
-      <c r="B34" t="s">
-        <v>50</v>
-      </c>
-      <c r="C34" t="s">
-        <v>75</v>
-      </c>
-      <c r="D34" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>76</v>
-      </c>
-      <c r="B35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" t="s">
-        <v>77</v>
-      </c>
-      <c r="D35" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>78</v>
-      </c>
-      <c r="B36" t="s">
-        <v>50</v>
-      </c>
-      <c r="C36" t="s">
-        <v>79</v>
-      </c>
-      <c r="D36" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>80</v>
-      </c>
-      <c r="B37" t="s">
-        <v>50</v>
-      </c>
-      <c r="C37" t="s">
-        <v>81</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="D57" t="s">
+        <v>105</v>
+      </c>
+      <c r="E57" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58" t="s">
+        <v>73</v>
+      </c>
+      <c r="D58" t="s">
+        <v>107</v>
+      </c>
+      <c r="E58" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>108</v>
+      </c>
+      <c r="C59" t="s">
+        <v>73</v>
+      </c>
+      <c r="D59" t="s">
+        <v>109</v>
+      </c>
+      <c r="E59" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>82</v>
-      </c>
-      <c r="B38" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" t="s">
-        <v>83</v>
-      </c>
-      <c r="D38" t="s">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B60" t="s">
+        <v>110</v>
+      </c>
+      <c r="C60" t="s">
+        <v>73</v>
+      </c>
+      <c r="D60" t="s">
+        <v>111</v>
+      </c>
+      <c r="E60" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B61" t="s">
+        <v>112</v>
+      </c>
+      <c r="C61" t="s">
+        <v>73</v>
+      </c>
+      <c r="D61" t="s">
+        <v>113</v>
+      </c>
+      <c r="E61" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B62" t="s">
+        <v>114</v>
+      </c>
+      <c r="C62" t="s">
+        <v>115</v>
+      </c>
+      <c r="D62" t="s">
+        <v>116</v>
+      </c>
+      <c r="E62" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B63" t="s">
+        <v>117</v>
+      </c>
+      <c r="C63" t="s">
+        <v>115</v>
+      </c>
+      <c r="D63" t="s">
+        <v>118</v>
+      </c>
+      <c r="E63" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B64" t="s">
+        <v>119</v>
+      </c>
+      <c r="C64" t="s">
+        <v>115</v>
+      </c>
+      <c r="D64" t="s">
+        <v>120</v>
+      </c>
+      <c r="E64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B65" t="s">
+        <v>121</v>
+      </c>
+      <c r="C65" t="s">
+        <v>115</v>
+      </c>
+      <c r="D65" t="s">
+        <v>122</v>
+      </c>
+      <c r="E65" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B66" t="s">
+        <v>123</v>
+      </c>
+      <c r="C66" t="s">
+        <v>115</v>
+      </c>
+      <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B67" t="s">
+        <v>125</v>
+      </c>
+      <c r="C67" t="s">
+        <v>115</v>
+      </c>
+      <c r="D67" t="s">
+        <v>126</v>
+      </c>
+      <c r="E67" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>84</v>
-      </c>
-      <c r="B39" t="s">
-        <v>50</v>
-      </c>
-      <c r="C39" t="s">
-        <v>85</v>
-      </c>
-      <c r="D39" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>86</v>
-      </c>
-      <c r="B40" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" t="s">
-        <v>87</v>
-      </c>
-      <c r="D40" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>88</v>
-      </c>
-      <c r="B41" t="s">
-        <v>50</v>
-      </c>
-      <c r="C41" t="s">
-        <v>89</v>
-      </c>
-      <c r="D41" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>90</v>
-      </c>
-      <c r="B42" t="s">
-        <v>91</v>
-      </c>
-      <c r="C42" t="s">
-        <v>92</v>
-      </c>
-      <c r="D42" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>93</v>
-      </c>
-      <c r="B43" t="s">
-        <v>91</v>
-      </c>
-      <c r="C43" t="s">
-        <v>94</v>
-      </c>
-      <c r="D43" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>95</v>
-      </c>
-      <c r="B44" t="s">
-        <v>91</v>
-      </c>
-      <c r="C44" t="s">
-        <v>96</v>
-      </c>
-      <c r="D44" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>97</v>
-      </c>
-      <c r="B45" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" t="s">
-        <v>98</v>
-      </c>
-      <c r="D45" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>99</v>
-      </c>
-      <c r="B46" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" t="s">
-        <v>100</v>
-      </c>
-      <c r="D46" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>101</v>
-      </c>
-      <c r="B47" t="s">
-        <v>91</v>
-      </c>
-      <c r="C47" t="s">
-        <v>102</v>
-      </c>
-      <c r="D47" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>103</v>
-      </c>
-      <c r="B48" t="s">
-        <v>91</v>
-      </c>
-      <c r="C48" t="s">
-        <v>104</v>
-      </c>
-      <c r="D48" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>106</v>
-      </c>
-      <c r="B49" t="s">
-        <v>91</v>
-      </c>
-      <c r="C49" t="s">
-        <v>107</v>
-      </c>
-      <c r="D49" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>108</v>
-      </c>
-      <c r="B50" t="s">
-        <v>91</v>
-      </c>
-      <c r="C50" t="s">
-        <v>109</v>
-      </c>
-      <c r="D50" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="126" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
-        <v>110</v>
-      </c>
-      <c r="B51" t="s">
-        <v>91</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D51" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
-        <v>112</v>
-      </c>
-      <c r="B52" t="s">
-        <v>91</v>
-      </c>
-      <c r="C52" t="s">
-        <v>113</v>
-      </c>
-      <c r="D52" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
-        <v>114</v>
-      </c>
-      <c r="B53" t="s">
-        <v>91</v>
-      </c>
-      <c r="C53" t="s">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B68" t="s">
+        <v>127</v>
+      </c>
+      <c r="C68" t="s">
         <v>115</v>
       </c>
-      <c r="D53" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
-        <v>116</v>
-      </c>
-      <c r="B54" t="s">
-        <v>91</v>
-      </c>
-      <c r="C54" t="s">
-        <v>117</v>
-      </c>
-      <c r="D54" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A55" t="s">
-        <v>118</v>
-      </c>
-      <c r="B55" t="s">
-        <v>91</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D55" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="144" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>120</v>
-      </c>
-      <c r="B56" t="s">
-        <v>91</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D56" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="162" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
-        <v>122</v>
-      </c>
-      <c r="B57" t="s">
-        <v>91</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D57" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
-        <v>124</v>
-      </c>
-      <c r="B58" t="s">
-        <v>91</v>
-      </c>
-      <c r="C58" t="s">
-        <v>125</v>
-      </c>
-      <c r="D58" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A59" t="s">
-        <v>126</v>
-      </c>
-      <c r="B59" t="s">
-        <v>91</v>
-      </c>
-      <c r="C59" t="s">
-        <v>127</v>
-      </c>
-      <c r="D59" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A60" t="s">
+      <c r="D68" t="s">
         <v>128</v>
       </c>
-      <c r="B60" t="s">
-        <v>91</v>
-      </c>
-      <c r="C60" t="s">
+      <c r="E68" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B69" t="s">
         <v>129</v>
       </c>
-      <c r="D60" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A61" t="s">
+      <c r="C69" t="s">
+        <v>115</v>
+      </c>
+      <c r="D69" t="s">
         <v>130</v>
       </c>
-      <c r="B61" t="s">
-        <v>91</v>
-      </c>
-      <c r="C61" t="s">
+      <c r="E69" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B70" t="s">
         <v>131</v>
       </c>
-      <c r="D61" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A62" t="s">
+      <c r="C70" t="s">
+        <v>115</v>
+      </c>
+      <c r="D70" t="s">
         <v>132</v>
       </c>
-      <c r="B62" t="s">
-        <v>133</v>
-      </c>
-      <c r="C62" t="s">
-        <v>134</v>
-      </c>
-      <c r="D62" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A63" t="s">
-        <v>135</v>
-      </c>
-      <c r="B63" t="s">
-        <v>133</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D63" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A64" t="s">
-        <v>137</v>
-      </c>
-      <c r="B64" t="s">
-        <v>133</v>
-      </c>
-      <c r="C64" t="s">
-        <v>138</v>
-      </c>
-      <c r="D64" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A65" t="s">
-        <v>139</v>
-      </c>
-      <c r="B65" t="s">
-        <v>133</v>
-      </c>
-      <c r="C65" t="s">
-        <v>140</v>
-      </c>
-      <c r="D65" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A66" t="s">
-        <v>141</v>
-      </c>
-      <c r="B66" t="s">
-        <v>133</v>
-      </c>
-      <c r="C66" t="s">
-        <v>142</v>
-      </c>
-      <c r="D66" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" t="s">
-        <v>143</v>
-      </c>
-      <c r="B67" t="s">
-        <v>133</v>
-      </c>
-      <c r="C67" t="s">
-        <v>144</v>
-      </c>
-      <c r="D67" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" t="s">
-        <v>145</v>
-      </c>
-      <c r="B68" t="s">
-        <v>133</v>
-      </c>
-      <c r="C68" t="s">
-        <v>146</v>
-      </c>
-      <c r="D68" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A69" t="s">
-        <v>147</v>
-      </c>
-      <c r="B69" t="s">
-        <v>133</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D69" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A70" t="s">
-        <v>149</v>
-      </c>
-      <c r="B70" t="s">
-        <v>133</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D70" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A71" t="s">
-        <v>151</v>
-      </c>
+      <c r="E70" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
         <v>133</v>
       </c>
       <c r="C71" t="s">
+        <v>115</v>
+      </c>
+      <c r="D71" t="s">
+        <v>134</v>
+      </c>
+      <c r="E71" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B72" t="s">
+        <v>135</v>
+      </c>
+      <c r="C72" t="s">
+        <v>115</v>
+      </c>
+      <c r="D72" t="s">
+        <v>136</v>
+      </c>
+      <c r="E72" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B73" t="s">
+        <v>137</v>
+      </c>
+      <c r="C73" t="s">
+        <v>115</v>
+      </c>
+      <c r="D73" t="s">
+        <v>138</v>
+      </c>
+      <c r="E73" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B74" t="s">
+        <v>139</v>
+      </c>
+      <c r="C74" t="s">
+        <v>115</v>
+      </c>
+      <c r="D74" t="s">
+        <v>140</v>
+      </c>
+      <c r="E74" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B75" t="s">
+        <v>141</v>
+      </c>
+      <c r="C75" t="s">
+        <v>115</v>
+      </c>
+      <c r="D75" t="s">
+        <v>142</v>
+      </c>
+      <c r="E75" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B76" t="s">
+        <v>143</v>
+      </c>
+      <c r="C76" t="s">
+        <v>115</v>
+      </c>
+      <c r="D76" t="s">
+        <v>144</v>
+      </c>
+      <c r="E76" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B77" t="s">
+        <v>145</v>
+      </c>
+      <c r="C77" t="s">
+        <v>115</v>
+      </c>
+      <c r="D77" t="s">
+        <v>146</v>
+      </c>
+      <c r="E77" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B78" t="s">
+        <v>147</v>
+      </c>
+      <c r="C78" t="s">
+        <v>115</v>
+      </c>
+      <c r="D78" t="s">
+        <v>148</v>
+      </c>
+      <c r="E78" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B79" t="s">
+        <v>149</v>
+      </c>
+      <c r="C79" t="s">
+        <v>115</v>
+      </c>
+      <c r="D79" t="s">
+        <v>150</v>
+      </c>
+      <c r="E79" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B80" t="s">
+        <v>151</v>
+      </c>
+      <c r="C80" t="s">
+        <v>115</v>
+      </c>
+      <c r="D80" t="s">
         <v>152</v>
       </c>
-      <c r="D71" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A72" t="s">
+      <c r="E80" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B81" t="s">
         <v>153</v>
       </c>
-      <c r="B72" t="s">
-        <v>133</v>
-      </c>
-      <c r="C72" t="s">
+      <c r="C81" t="s">
+        <v>115</v>
+      </c>
+      <c r="D81" t="s">
         <v>154</v>
       </c>
-      <c r="D72" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A73" t="s">
+      <c r="E81" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B82" t="s">
         <v>155</v>
       </c>
-      <c r="B73" t="s">
-        <v>133</v>
-      </c>
-      <c r="C73" t="s">
+      <c r="C82" t="s">
         <v>156</v>
       </c>
-      <c r="D73" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A74" t="s">
+      <c r="D82" t="s">
         <v>157</v>
       </c>
-      <c r="B74" t="s">
-        <v>133</v>
-      </c>
-      <c r="C74" s="1" t="s">
+      <c r="E82" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B83" t="s">
         <v>158</v>
       </c>
-      <c r="D74" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" t="s">
+      <c r="C83" t="s">
+        <v>156</v>
+      </c>
+      <c r="D83" t="s">
         <v>159</v>
       </c>
-      <c r="B75" t="s">
-        <v>133</v>
-      </c>
-      <c r="C75" t="s">
+      <c r="E83" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B84" t="s">
         <v>160</v>
       </c>
-      <c r="D75" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A76" t="s">
+      <c r="C84" t="s">
+        <v>156</v>
+      </c>
+      <c r="D84" t="s">
         <v>161</v>
       </c>
-      <c r="B76" t="s">
-        <v>133</v>
-      </c>
-      <c r="C76" t="s">
+      <c r="E84" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B85" t="s">
         <v>162</v>
       </c>
-      <c r="D76" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A77" t="s">
+      <c r="C85" t="s">
+        <v>156</v>
+      </c>
+      <c r="D85" t="s">
         <v>163</v>
       </c>
-      <c r="B77" t="s">
-        <v>133</v>
-      </c>
-      <c r="C77" s="1" t="s">
+      <c r="E85" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B86" t="s">
         <v>164</v>
       </c>
-      <c r="D77" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A78" t="s">
+      <c r="C86" t="s">
+        <v>156</v>
+      </c>
+      <c r="D86" t="s">
         <v>165</v>
       </c>
-      <c r="B78" t="s">
-        <v>133</v>
-      </c>
-      <c r="C78" t="s">
+      <c r="E86" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B87" t="s">
         <v>166</v>
       </c>
-      <c r="D78" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A79" t="s">
+      <c r="C87" t="s">
+        <v>156</v>
+      </c>
+      <c r="D87" t="s">
         <v>167</v>
       </c>
-      <c r="B79" t="s">
-        <v>133</v>
-      </c>
-      <c r="C79" t="s">
+      <c r="E87" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B88" t="s">
         <v>168</v>
       </c>
-      <c r="D79" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A80" t="s">
+      <c r="C88" t="s">
+        <v>156</v>
+      </c>
+      <c r="D88" t="s">
         <v>169</v>
       </c>
-      <c r="B80" t="s">
-        <v>133</v>
-      </c>
-      <c r="C80" t="s">
+      <c r="E88" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B89" t="s">
         <v>170</v>
       </c>
-      <c r="D80" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A81" t="s">
+      <c r="C89" t="s">
+        <v>156</v>
+      </c>
+      <c r="D89" t="s">
         <v>171</v>
       </c>
-      <c r="B81" t="s">
-        <v>133</v>
-      </c>
-      <c r="C81" t="s">
+      <c r="E89" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B90" t="s">
         <v>172</v>
       </c>
-      <c r="D81" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A82" t="s">
+      <c r="C90" t="s">
+        <v>156</v>
+      </c>
+      <c r="D90" t="s">
         <v>173</v>
       </c>
-      <c r="B82" t="s">
-        <v>174</v>
-      </c>
-      <c r="C82" t="s">
-        <v>175</v>
-      </c>
-      <c r="D82" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A83" t="s">
-        <v>176</v>
-      </c>
-      <c r="B83" t="s">
-        <v>174</v>
-      </c>
-      <c r="C83" t="s">
-        <v>177</v>
-      </c>
-      <c r="D83" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A84" t="s">
-        <v>178</v>
-      </c>
-      <c r="B84" t="s">
-        <v>174</v>
-      </c>
-      <c r="C84" t="s">
-        <v>179</v>
-      </c>
-      <c r="D84" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A85" t="s">
-        <v>180</v>
-      </c>
-      <c r="B85" t="s">
-        <v>174</v>
-      </c>
-      <c r="C85" t="s">
-        <v>181</v>
-      </c>
-      <c r="D85" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A86" t="s">
-        <v>182</v>
-      </c>
-      <c r="B86" t="s">
-        <v>174</v>
-      </c>
-      <c r="C86" t="s">
-        <v>183</v>
-      </c>
-      <c r="D86" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A87" t="s">
-        <v>184</v>
-      </c>
-      <c r="B87" t="s">
-        <v>174</v>
-      </c>
-      <c r="C87" t="s">
-        <v>185</v>
-      </c>
-      <c r="D87" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A88" t="s">
-        <v>186</v>
-      </c>
-      <c r="B88" t="s">
-        <v>174</v>
-      </c>
-      <c r="C88" t="s">
-        <v>187</v>
-      </c>
-      <c r="D88" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A89" t="s">
-        <v>188</v>
-      </c>
-      <c r="B89" t="s">
-        <v>174</v>
-      </c>
-      <c r="C89" t="s">
-        <v>189</v>
-      </c>
-      <c r="D89" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A90" t="s">
-        <v>190</v>
-      </c>
-      <c r="B90" t="s">
-        <v>174</v>
-      </c>
-      <c r="C90" t="s">
-        <v>191</v>
-      </c>
-      <c r="D90" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A91" t="s">
-        <v>192</v>
-      </c>
+      <c r="E90" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B91" t="s">
         <v>174</v>
       </c>
       <c r="C91" t="s">
+        <v>156</v>
+      </c>
+      <c r="D91" t="s">
+        <v>175</v>
+      </c>
+      <c r="E91" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B92" t="s">
+        <v>176</v>
+      </c>
+      <c r="C92" t="s">
+        <v>156</v>
+      </c>
+      <c r="D92" t="s">
+        <v>177</v>
+      </c>
+      <c r="E92" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B93" t="s">
+        <v>178</v>
+      </c>
+      <c r="C93" t="s">
+        <v>156</v>
+      </c>
+      <c r="D93" t="s">
+        <v>179</v>
+      </c>
+      <c r="E93" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B94" t="s">
+        <v>180</v>
+      </c>
+      <c r="C94" t="s">
+        <v>156</v>
+      </c>
+      <c r="D94" t="s">
+        <v>181</v>
+      </c>
+      <c r="E94" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B95" t="s">
+        <v>182</v>
+      </c>
+      <c r="C95" t="s">
+        <v>156</v>
+      </c>
+      <c r="D95" t="s">
+        <v>183</v>
+      </c>
+      <c r="E95" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B96" t="s">
+        <v>184</v>
+      </c>
+      <c r="C96" t="s">
+        <v>156</v>
+      </c>
+      <c r="D96" t="s">
+        <v>185</v>
+      </c>
+      <c r="E96" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B97" t="s">
+        <v>186</v>
+      </c>
+      <c r="C97" t="s">
+        <v>156</v>
+      </c>
+      <c r="D97" t="s">
+        <v>187</v>
+      </c>
+      <c r="E97" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B98" t="s">
+        <v>188</v>
+      </c>
+      <c r="C98" t="s">
+        <v>156</v>
+      </c>
+      <c r="D98" t="s">
+        <v>189</v>
+      </c>
+      <c r="E98" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B99" t="s">
+        <v>190</v>
+      </c>
+      <c r="C99" t="s">
+        <v>156</v>
+      </c>
+      <c r="D99" t="s">
+        <v>191</v>
+      </c>
+      <c r="E99" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B100" t="s">
+        <v>192</v>
+      </c>
+      <c r="C100" t="s">
+        <v>156</v>
+      </c>
+      <c r="D100" t="s">
         <v>193</v>
       </c>
-      <c r="D91" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A92" t="s">
+      <c r="E100" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B101" t="s">
         <v>194</v>
       </c>
-      <c r="B92" t="s">
-        <v>174</v>
-      </c>
-      <c r="C92" s="1" t="s">
+      <c r="C101" t="s">
+        <v>156</v>
+      </c>
+      <c r="D101" t="s">
         <v>195</v>
       </c>
-      <c r="D92" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A93" t="s">
-        <v>196</v>
-      </c>
-      <c r="B93" t="s">
-        <v>174</v>
-      </c>
-      <c r="C93" t="s">
-        <v>197</v>
-      </c>
-      <c r="D93" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A94" t="s">
-        <v>198</v>
-      </c>
-      <c r="B94" t="s">
-        <v>174</v>
-      </c>
-      <c r="C94" t="s">
-        <v>199</v>
-      </c>
-      <c r="D94" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A95" t="s">
-        <v>200</v>
-      </c>
-      <c r="B95" t="s">
-        <v>174</v>
-      </c>
-      <c r="C95" t="s">
-        <v>201</v>
-      </c>
-      <c r="D95" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A96" t="s">
-        <v>202</v>
-      </c>
-      <c r="B96" t="s">
-        <v>174</v>
-      </c>
-      <c r="C96" t="s">
-        <v>203</v>
-      </c>
-      <c r="D96" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A97" t="s">
-        <v>204</v>
-      </c>
-      <c r="B97" t="s">
-        <v>174</v>
-      </c>
-      <c r="C97" t="s">
-        <v>205</v>
-      </c>
-      <c r="D97" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="126" x14ac:dyDescent="0.45">
-      <c r="A98" t="s">
-        <v>206</v>
-      </c>
-      <c r="B98" t="s">
-        <v>174</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D98" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="342" x14ac:dyDescent="0.45">
-      <c r="A99" t="s">
-        <v>208</v>
-      </c>
-      <c r="B99" t="s">
-        <v>174</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D99" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A100" t="s">
-        <v>210</v>
-      </c>
-      <c r="B100" t="s">
-        <v>174</v>
-      </c>
-      <c r="C100" t="s">
-        <v>211</v>
-      </c>
-      <c r="D100" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A101" t="s">
-        <v>212</v>
-      </c>
-      <c r="B101" t="s">
-        <v>174</v>
-      </c>
-      <c r="C101" t="s">
-        <v>213</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E101" xr:uid="{CA116F4C-F3D0-4267-A97A-F82C571EBE6D}"/>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
